--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487740_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487740_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3145</v>
+        <v>5.9361</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5667</v>
+        <v>3.788</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7477</v>
+        <v>2.1481</v>
       </c>
       <c r="G2" t="n">
         <v>3.6634</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2048</v>
+        <v>-0.1735</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1508</v>
+        <v>-0.9295</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3556</v>
+        <v>0.756</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.389</v>
+        <v>1.5468</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1258</v>
+        <v>0.1956</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5148</v>
+        <v>1.3513</v>
       </c>
       <c r="G3" t="n">
         <v>1.1498</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0608</v>
+        <v>0.097</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0296</v>
+        <v>-0.7083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9688</v>
+        <v>0.8053</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8917</v>
+        <v>0.919</v>
       </c>
       <c r="E4" t="n">
         <v>1.2185</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3268</v>
+        <v>-0.2996</v>
       </c>
       <c r="G4" t="n">
         <v>1.0676</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1759</v>
+        <v>-0.1486</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6754</v>
+        <v>0.8028</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7229</v>
+        <v>0.823</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0475</v>
+        <v>-0.0202</v>
       </c>
       <c r="G5" t="n">
         <v>1.4457</v>
@@ -844,13 +844,13 @@
         <v>0.194</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7703</v>
+        <v>-0.6429</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3191</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1047</v>
+        <v>0.2979</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0017</v>
+        <v>-0.9807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.897</v>
+        <v>1.2786</v>
       </c>
       <c r="G6" t="n">
         <v>0.9407</v>
@@ -922,13 +922,13 @@
         <v>2.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5514</v>
+        <v>-1.1488</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0768</v>
+        <v>-1.0557</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4746</v>
+        <v>-0.0931</v>
       </c>
       <c r="V6" t="n">
         <v>0.894</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.245</v>
+        <v>-0.1994</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3723</v>
+        <v>-1.2722</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1273</v>
+        <v>1.0728</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3757</v>
@@ -1000,13 +1000,13 @@
         <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7037</v>
+        <v>-0.6581</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.775</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0168</v>
       </c>
       <c r="V7" t="n">
         <v>0.2821</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2402</v>
+        <v>-1.1323</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1843</v>
+        <v>0.678</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9441000000000001</v>
+        <v>-1.8104</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8771</v>
+        <v>-0.7306</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9195</v>
+        <v>-1.6354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9576</v>
+        <v>0.9048</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1172</v>
+        <v>1.992</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7744</v>
+        <v>0.1195</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6573</v>
+        <v>1.8725</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9943</v>
+        <v>-2.7225</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6939</v>
+        <v>-1.7549</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3004</v>
+        <v>-0.9677</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3881</v>
+        <v>2.5224</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2488</v>
+        <v>-1.7003</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1672</v>
+        <v>-1.1199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4159</v>
+        <v>-0.5804</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5839</v>
+        <v>-1.8623</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4173</v>
+        <v>-0.0599</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0011</v>
+        <v>-1.8023</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7306</v>
+        <v>-0.0113</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6354</v>
+        <v>-0.0519</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9048</v>
+        <v>0.0406</v>
       </c>
       <c r="J9" t="n">
-        <v>1.992</v>
+        <v>0.0612</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1195</v>
+        <v>0.0206</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8725</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7225</v>
+        <v>-0.0725</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7549</v>
+        <v>-0.0725</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9677</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5224</v>
+        <v>0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7164</v>
+        <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1519</v>
+        <v>-0.2092</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3807</v>
+        <v>-0.1211</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7712</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8895</v>
+        <v>-2.1802</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0599</v>
+        <v>-2.8245</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8296</v>
+        <v>0.6443</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0113</v>
+        <v>-1.8771</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0519</v>
+        <v>-0.9195</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0406</v>
+        <v>-0.9576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0612</v>
+        <v>0.1172</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0206</v>
+        <v>0.7744</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0406</v>
+        <v>-0.6573</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0725</v>
+        <v>-1.9943</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0725</v>
+        <v>-1.6939</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.3004</v>
       </c>
       <c r="P10" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="R10" t="n">
-        <v>0.194</v>
+        <v>2.5224</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2364</v>
+        <v>-0.6912</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1211</v>
+        <v>-0.8073</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1153</v>
+        <v>0.1161</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2198</v>
+        <v>-3.8901</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6795</v>
+        <v>-3.7586</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5403</v>
+        <v>-0.1315</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7136</v>
@@ -1312,13 +1312,13 @@
         <v>2.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.642</v>
+        <v>-1.3122</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1497</v>
+        <v>-1.2287</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4923</v>
+        <v>-0.0835</v>
       </c>
       <c r="V11" t="n">
         <v>0.3299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9272</v>
+        <v>-5.5724</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9157</v>
+        <v>-1.6154</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0116</v>
+        <v>-3.9571</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2561</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1638</v>
+        <v>-0.8089</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8356</v>
+        <v>-0.5353</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3282</v>
+        <v>-0.2736</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0597</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9397</v>
+        <v>-5.334100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4138</v>
+        <v>-3.8082</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.525999999999999</v>
+        <v>-1.526000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6972</v>
+        <v>-1.697199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.366600000000002</v>
+        <v>-4.366600000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6693</v>
+        <v>2.669299999999999</v>
       </c>
       <c r="J13" t="n">
         <v>12.1722</v>
@@ -1447,19 +1447,19 @@
         <v>5.248200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>6.924</v>
+        <v>6.923999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-13.8693</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.614699999999999</v>
+        <v>-9.614700000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-4.2547</v>
       </c>
       <c r="P13" t="n">
-        <v>7.761399999999999</v>
+        <v>7.7614</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.6717</v>
@@ -1468,13 +1468,13 @@
         <v>18.433</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.002599999999999</v>
+        <v>-7.396700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-8.171100000000001</v>
+        <v>-7.5652</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1684999999999999</v>
+        <v>0.1685</v>
       </c>
       <c r="V13" t="n">
         <v>-4.0015</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9324</v>
+        <v>4.1734</v>
       </c>
       <c r="E14" t="n">
-        <v>5.512</v>
+        <v>3.8103</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4204</v>
+        <v>0.3631</v>
       </c>
       <c r="G14" t="n">
         <v>3.6355</v>
@@ -1546,13 +1546,13 @@
         <v>1.9403</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6447</v>
+        <v>1.8856</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1982</v>
+        <v>0.4965</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4464</v>
+        <v>1.3891</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3776</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5314</v>
+        <v>3.0284</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0299</v>
+        <v>1.7213</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5015</v>
+        <v>1.3071</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6049</v>
+        <v>0.3862</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.0753</v>
+        <v>0.5775</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4705</v>
+        <v>-0.1913</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7962</v>
+        <v>1.4726</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8774</v>
+        <v>0.6962</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.7764</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8087</v>
+        <v>-1.0863</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1979</v>
+        <v>-0.1187</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3893</v>
+        <v>-0.9677</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8244</v>
+        <v>0.3124</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6202</v>
+        <v>-0.6169</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2042</v>
+        <v>0.9292</v>
       </c>
       <c r="V15" t="n">
-        <v>1.506</v>
+        <v>1.5537</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1761</v>
+        <v>1.8358</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3299</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1647</v>
+        <v>1.5335</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3209</v>
+        <v>-1.0255</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8438</v>
+        <v>2.559</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3862</v>
+        <v>1.3577</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5775</v>
+        <v>-0.8173</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1913</v>
+        <v>2.175</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4726</v>
+        <v>2.1831</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6962</v>
+        <v>-0.4202</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7764</v>
+        <v>2.6032</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0863</v>
+        <v>-0.8254</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1187</v>
+        <v>-0.3971</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9677</v>
+        <v>-0.4282</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7761</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5514</v>
+        <v>1.146</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0173</v>
+        <v>-0.2981</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4659</v>
+        <v>1.4441</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5537</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8358</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7689</v>
+        <v>1.0042</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9264</v>
+        <v>-0.5707</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6953</v>
+        <v>1.5748</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3577</v>
+        <v>-1.6049</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8173</v>
+        <v>-2.0753</v>
       </c>
       <c r="I17" t="n">
-        <v>2.175</v>
+        <v>0.4705</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1831</v>
+        <v>-0.7962</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4202</v>
+        <v>-0.8774</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6032</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8254</v>
+        <v>-0.8087</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3971</v>
+        <v>-1.1979</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4282</v>
+        <v>0.3893</v>
       </c>
       <c r="P17" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3813</v>
+        <v>1.2971</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.199</v>
+        <v>0.0196</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5803</v>
+        <v>1.2775</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1761</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5039</v>
+        <v>0.2905</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8497</v>
+        <v>-0.8324</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3458</v>
+        <v>1.1229</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4018</v>
+        <v>-0.6577</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9664</v>
+        <v>0.7637</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4354</v>
+        <v>-1.4214</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0714</v>
+        <v>0.3394</v>
       </c>
       <c r="K18" t="n">
-        <v>1.001</v>
+        <v>0.9434</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0704</v>
+        <v>-0.6039</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6696</v>
+        <v>-0.9971</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0346</v>
+        <v>-0.1796</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.635</v>
+        <v>-0.8175</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0424</v>
+        <v>0.3766</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1828</v>
+        <v>-0.2016</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8596</v>
+        <v>0.5782</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0549</v>
+        <v>0.119</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9325</v>
+        <v>1.5494</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8776</v>
+        <v>-1.4304</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6577</v>
+        <v>1.4018</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7637</v>
+        <v>0.9664</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4214</v>
+        <v>0.4354</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3394</v>
+        <v>3.0714</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9434</v>
+        <v>1.001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6039</v>
+        <v>2.0704</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9971</v>
+        <v>-1.6696</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1796</v>
+        <v>-0.0346</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8175</v>
+        <v>-1.635</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0312</v>
+        <v>0.6575</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3017</v>
+        <v>-0.1175</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3329</v>
+        <v>0.775</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3776</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8989</v>
+        <v>0.017</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2234</v>
+        <v>0.4773</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6755</v>
+        <v>-0.4603</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2316</v>
@@ -2014,13 +2014,13 @@
         <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0554</v>
+        <v>0.8605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4845</v>
+        <v>0.2162</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4291</v>
+        <v>0.6444</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3827</v>
+        <v>-1.3215</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8247</v>
+        <v>-0.2241</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5579</v>
+        <v>-1.0974</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8823</v>
@@ -2092,13 +2092,13 @@
         <v>0.3881</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6063</v>
+        <v>0.4548</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.424</v>
+        <v>0.1766</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1824</v>
+        <v>0.2782</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2821</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6251</v>
+        <v>-2.2374</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2796</v>
+        <v>-3.3797</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6546</v>
+        <v>1.1423</v>
       </c>
       <c r="G22" t="n">
         <v>0.2924</v>
@@ -2170,13 +2170,13 @@
         <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2916</v>
+        <v>1.6793</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2568</v>
+        <v>0.1567</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0348</v>
+        <v>1.5226</v>
       </c>
       <c r="V22" t="n">
         <v>1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.939700000000002</v>
+        <v>6.6071</v>
       </c>
       <c r="E23" t="n">
-        <v>1.525899999999999</v>
+        <v>1.5259</v>
       </c>
       <c r="F23" t="n">
-        <v>4.414000000000001</v>
+        <v>5.081100000000001</v>
       </c>
       <c r="G23" t="n">
         <v>1.6971</v>
@@ -2248,13 +2248,13 @@
         <v>10.6718</v>
       </c>
       <c r="S23" t="n">
-        <v>8.0025</v>
+        <v>8.6698</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1685000000000005</v>
+        <v>-0.1684999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>8.1708</v>
+        <v>8.8383</v>
       </c>
       <c r="V23" t="n">
         <v>4.0015</v>
